--- a/db/A7XLK-4104-Jewelry.xlsx
+++ b/db/A7XLK-4104-Jewelry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F80E1D-0E1D-474F-B588-0F2E052A4EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B102DF-B534-854D-9ECB-EAA236F270E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="5200" windowWidth="28260" windowHeight="17560" xr2:uid="{2B2AD4FA-9B91-2346-8F8C-40168F957E39}"/>
+    <workbookView xWindow="14960" yWindow="7080" windowWidth="28260" windowHeight="17560" xr2:uid="{2B2AD4FA-9B91-2346-8F8C-40168F957E39}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -83,10 +83,6 @@
     <t>107</t>
   </si>
   <si>
-    <t>fig/XLK-415-OnlineShopping/A7XLK-415-Jewelry-01.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Lionmango</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,15 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fig/XLK-415-OnlineShopping/A7XLK-415-Jewelry-03.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-415-OnlineShopping/A7XLK-415-Jewelry-05.png</t>
-  </si>
-  <si>
-    <t>fig/XLK-415-OnlineShopping/A7XLK-415-Jewelry-07.png</t>
-  </si>
-  <si>
     <t>https://www.vacanza.com.tw/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,10 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fig/XLK-415-OnlineShopping/A7XLK-415-Jewelry-02.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.facebook.com/VacanzaLife</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,14 +159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fig/XLK-415-OnlineShopping/A7XLK-415-Jewelry-06.jpeg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-415-OnlineShopping/A7XLK-415-Jewelry-04.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.bluenile.com/tw/jewelry/search</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -193,6 +168,34 @@
   </si>
   <si>
     <t>https://www.facebook.com/bluenile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-414-OnlineShopping/A7XLK-415-Jewelry-01.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-414-OnlineShopping/A7XLK-415-Jewelry-02.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-414-OnlineShopping/A7XLK-415-Jewelry-03.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-414-OnlineShopping/A7XLK-415-Jewelry-04.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-414-OnlineShopping/A7XLK-415-Jewelry-05.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-414-OnlineShopping/A7XLK-415-Jewelry-06.jpeg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-414-OnlineShopping/A7XLK-415-Jewelry-07.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -620,7 +623,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -631,16 +634,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -651,16 +654,16 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -671,16 +674,16 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -691,16 +694,16 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -711,16 +714,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -731,16 +734,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -751,16 +754,16 @@
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
